--- a/tabular/genus/amdo-refseqs-side-data.xlsx
+++ b/tabular/genus/amdo-refseqs-side-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robertgifford/Projects/virus/comparative/DNA/Parvovirus-GLUE/tabular/genus/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/diversity/Parvovirus-GLUE/tabular/genus/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD47251F-56C4-E544-8511-D59A8CE457EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA3B8740-455F-4C49-B8E8-847E7AD60129}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18480" yWindow="7440" windowWidth="28040" windowHeight="17440" xr2:uid="{469403FE-80B6-3840-B15B-8B62EF5C2974}"/>
+    <workbookView xWindow="880" yWindow="500" windowWidth="27920" windowHeight="17500" xr2:uid="{469403FE-80B6-3840-B15B-8B62EF5C2974}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -284,7 +284,32 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF660066"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -295,6 +320,30 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2991AD1-C189-2245-B51C-58D8D3C62132}" name="Table1" displayName="Table1" ref="A1:O9" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:O9" xr:uid="{CF3A7407-E202-894C-A9A7-DB3CEAB96388}"/>
+  <tableColumns count="15">
+    <tableColumn id="1" xr3:uid="{146A080F-FD99-C84C-8183-B3A5ED8AEF24}" name="sequenceID"/>
+    <tableColumn id="2" xr3:uid="{3B6749DA-7179-6346-9315-05DBB874ED16}" name="virus_name"/>
+    <tableColumn id="3" xr3:uid="{4F47587E-E7A1-5F48-8398-D5D3D88DB127}" name="virus_subfamily"/>
+    <tableColumn id="4" xr3:uid="{642BE083-15B6-1748-A2F1-B3B4B2035CCD}" name="virus_full_name"/>
+    <tableColumn id="5" xr3:uid="{7D966DC2-B08E-E740-91DB-D7D31D8CB8DE}" name="virus_other_name"/>
+    <tableColumn id="6" xr3:uid="{C7FCE498-900B-424E-8F83-6578530A7119}" name="host_species"/>
+    <tableColumn id="7" xr3:uid="{DA611F6E-6FC0-084C-9EC2-E31DEA2AD8C4}" name="virus_genus"/>
+    <tableColumn id="8" xr3:uid="{FD3CC313-F938-2649-9CA0-D6CC0D134694}" name="assign_clade"/>
+    <tableColumn id="9" xr3:uid="{5528BB2F-23DC-334F-AB04-D865537276DB}" name="assign_subclade"/>
+    <tableColumn id="10" xr3:uid="{004F5790-FDA2-DF41-93AB-2454DD852F4F}" name="virus_clade_ns"/>
+    <tableColumn id="11" xr3:uid="{0472BFB6-FE7E-F84A-BE4B-17584EE04787}" name="virus_subclade_ns"/>
+    <tableColumn id="12" xr3:uid="{7F4196D2-6D33-CC45-BBD2-FE1B1652BC5D}" name="virus_clade_vp"/>
+    <tableColumn id="13" xr3:uid="{1DE18775-5BC2-C84A-B04C-B6D88FC3ADD7}" name="virus_subclade_vp"/>
+    <tableColumn id="14" xr3:uid="{EDF932E3-8DEE-1A41-829C-C589E3914C29}" name="lab_construct"/>
+    <tableColumn id="15" xr3:uid="{FA6CA12B-CEA1-9B48-BF54-1734F668DF7F}" name="accession-other"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -597,11 +646,21 @@
   <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="13.1640625" customWidth="1"/>
     <col min="3" max="3" width="22.1640625" customWidth="1"/>
     <col min="4" max="4" width="33.33203125" customWidth="1"/>
     <col min="5" max="5" width="29.83203125" customWidth="1"/>
     <col min="6" max="6" width="19.5" customWidth="1"/>
     <col min="7" max="7" width="20.1640625" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="16.83203125" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="12" width="15.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.5" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.2">
@@ -1030,5 +1089,8 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>